--- a/Export/R0.3/2025-08-02/BoM/ESPNut-D1-R0.3-BoM-XLS-02082025-1.xlsx
+++ b/Export/R0.3/2025-08-02/BoM/ESPNut-D1-R0.3-BoM-XLS-02082025-1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="144">
   <si>
     <t>#</t>
   </si>
@@ -128,10 +128,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>D1,D4,D5</t>
-  </si>
-  <si>
-    <t>RX_LED,TX_LED,VBUS_LED</t>
+    <t>D1</t>
   </si>
   <si>
     <t>VBUS_LED</t>
@@ -182,6 +179,30 @@
     <t>8</t>
   </si>
   <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>RX_LED</t>
+  </si>
+  <si>
+    <t>19-213/BHC-ZL1M2RY/3T</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>TX_LED</t>
+  </si>
+  <si>
+    <t>19-217/R6C-AL1M2VY/3T</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>H1,H2,J2,J3,J5,JP1,JP2,JP3,JP4,JP5,JP6,JP7,TP1,TP2,TP3,TP4,TP5,TP6,TP7,TP8,TP9,TP10,TP11</t>
   </si>
   <si>
@@ -200,7 +221,7 @@
     <t>YES</t>
   </si>
   <si>
-    <t>9</t>
+    <t>11</t>
   </si>
   <si>
     <t>J1</t>
@@ -221,7 +242,7 @@
     <t>Yi Yuan</t>
   </si>
   <si>
-    <t>10</t>
+    <t>12</t>
   </si>
   <si>
     <t>J4</t>
@@ -239,7 +260,7 @@
     <t>JST</t>
   </si>
   <si>
-    <t>11</t>
+    <t>13</t>
   </si>
   <si>
     <t>Q1,Q2</t>
@@ -254,7 +275,7 @@
     <t>Diodes Incorporated</t>
   </si>
   <si>
-    <t>12</t>
+    <t>14</t>
   </si>
   <si>
     <t>Q3,Q4</t>
@@ -263,7 +284,7 @@
     <t>MMBT3906T-7-F</t>
   </si>
   <si>
-    <t>13</t>
+    <t>15</t>
   </si>
   <si>
     <t>R1,R14,R17,R18</t>
@@ -278,7 +299,7 @@
     <t>RC0402FR-7D220RL</t>
   </si>
   <si>
-    <t>14</t>
+    <t>16</t>
   </si>
   <si>
     <t>R2,R5</t>
@@ -290,7 +311,7 @@
     <t>WR04X5101FTL</t>
   </si>
   <si>
-    <t>15</t>
+    <t>17</t>
   </si>
   <si>
     <t>R3,R4,R7,R10</t>
@@ -302,7 +323,7 @@
     <t>WR04X1002FTL</t>
   </si>
   <si>
-    <t>16</t>
+    <t>18</t>
   </si>
   <si>
     <t>R6,R8,R15,R16</t>
@@ -314,7 +335,7 @@
     <t>WR04X1001FTL</t>
   </si>
   <si>
-    <t>17</t>
+    <t>19</t>
   </si>
   <si>
     <t>R11</t>
@@ -323,13 +344,13 @@
     <t>RC0402FR-0710KL</t>
   </si>
   <si>
-    <t>18</t>
+    <t>20</t>
   </si>
   <si>
     <t>R12</t>
   </si>
   <si>
-    <t>19</t>
+    <t>21</t>
   </si>
   <si>
     <t>SW1,SW2,SW5</t>
@@ -350,7 +371,7 @@
     <t>BX-TS-26-3425TP</t>
   </si>
   <si>
-    <t>20</t>
+    <t>22</t>
   </si>
   <si>
     <t>SW3,SW4</t>
@@ -368,9 +389,6 @@
     <t>C&amp;K</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>U1</t>
   </si>
   <si>
@@ -389,7 +407,7 @@
     <t>CH340C</t>
   </si>
   <si>
-    <t>22</t>
+    <t>24</t>
   </si>
   <si>
     <t>U2</t>
@@ -407,6 +425,9 @@
     <t>Microchip</t>
   </si>
   <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>U3</t>
   </si>
   <si>
@@ -422,7 +443,7 @@
     <t>Diodes Inc</t>
   </si>
   <si>
-    <t>24</t>
+    <t>26</t>
   </si>
   <si>
     <t>Y1</t>
@@ -1439,13 +1460,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="33.2752293577982" customWidth="1"/>
+    <col min="4" max="4" width="33.8990825688073" customWidth="1"/>
     <col min="5" max="5" width="62" customWidth="1"/>
     <col min="6" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="31" customWidth="1"/>
@@ -1624,22 +1645,22 @@
         <v>34</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -1647,19 +1668,19 @@
     </row>
     <row r="7" ht="50" customHeight="1" spans="1:10">
       <c r="A7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>10</v>
@@ -1668,10 +1689,10 @@
         <v>13</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -1679,19 +1700,19 @@
     </row>
     <row r="8" ht="50" customHeight="1" spans="1:10">
       <c r="A8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>10</v>
@@ -1700,62 +1721,62 @@
         <v>13</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1" spans="1:10">
+      <c r="A9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="169" customHeight="1" spans="1:10">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" s="4" t="s">
+      <c r="I9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" ht="50" customHeight="1" spans="1:10">
       <c r="A10" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>10</v>
@@ -1764,74 +1785,74 @@
         <v>13</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="177" customHeight="1" spans="1:10">
+      <c r="A11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="G11" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" ht="50" customHeight="1" spans="1:10">
-      <c r="A11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="J11" s="3" t="s">
+      <c r="H11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J11" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" ht="50" customHeight="1" spans="1:10">
       <c r="A12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
@@ -1839,31 +1860,31 @@
     </row>
     <row r="13" ht="50" customHeight="1" spans="1:10">
       <c r="A13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="I13" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>13</v>
@@ -1871,31 +1892,31 @@
     </row>
     <row r="14" ht="50" customHeight="1" spans="1:10">
       <c r="A14" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -1903,19 +1924,19 @@
     </row>
     <row r="15" ht="50" customHeight="1" spans="1:10">
       <c r="A15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="D15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>15</v>
@@ -1924,10 +1945,10 @@
         <v>13</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>13</v>
@@ -1935,19 +1956,19 @@
     </row>
     <row r="16" ht="50" customHeight="1" spans="1:10">
       <c r="A16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>26</v>
@@ -1956,10 +1977,10 @@
         <v>13</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -1967,28 +1988,28 @@
     </row>
     <row r="17" ht="50" customHeight="1" spans="1:10">
       <c r="A17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>25</v>
@@ -1999,22 +2020,22 @@
     </row>
     <row r="18" ht="50" customHeight="1" spans="1:10">
       <c r="A18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="D18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>13</v>
@@ -2023,62 +2044,62 @@
         <v>97</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="50" customHeight="1" spans="1:10">
-      <c r="A19" s="4" t="s">
+    <row r="19" ht="50" customHeight="1" spans="1:10">
+      <c r="A19" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="4" t="s">
+      <c r="C19" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="20" ht="50" customHeight="1" spans="1:10">
       <c r="A20" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>13</v>
@@ -2087,103 +2108,103 @@
         <v>104</v>
       </c>
       <c r="I20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="50" customHeight="1" spans="1:10">
+      <c r="A21" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="21" ht="50" customHeight="1" spans="1:10">
-      <c r="A21" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="J21" s="3" t="s">
+      <c r="C21" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" ht="50" customHeight="1" spans="1:10">
       <c r="A22" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="23" ht="50" customHeight="1" spans="1:10">
       <c r="A23" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>13</v>
@@ -2191,19 +2212,19 @@
     </row>
     <row r="24" ht="50" customHeight="1" spans="1:10">
       <c r="A24" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>10</v>
@@ -2212,30 +2233,30 @@
         <v>13</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" ht="50" customHeight="1" spans="1:10">
       <c r="A25" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>13</v>
+        <v>129</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>10</v>
@@ -2244,12 +2265,76 @@
         <v>13</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" ht="50" customHeight="1" spans="1:10">
+      <c r="A26" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="I26" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" ht="50" customHeight="1" spans="1:10">
+      <c r="A27" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>13</v>
       </c>
     </row>
